--- a/public/document/template_rekap utk uang.xlsx
+++ b/public/document/template_rekap utk uang.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rifqind\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xampp\htdocs\singkat\public\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{175F1512-4657-49AC-9F3E-9E5DA5CB7F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6203DA79-8DD0-41F1-84FE-0A8712AF585E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8D25137E-22AB-4F2F-8C7D-B798D3086879}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>NIP Lama</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>HL16</t>
+  </si>
+  <si>
+    <t>Nama Pegawai</t>
   </si>
 </sst>
 </file>
@@ -169,9 +172,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,95 +511,101 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D4FBC0C-A289-4C36-B824-9B1CC430D4CC}">
-  <dimension ref="A1:AC1"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="8.88671875" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
